--- a/artfynd/A 53513-2019 artfynd.xlsx
+++ b/artfynd/A 53513-2019 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031681</v>
+        <v>122031210</v>
       </c>
       <c r="B3" t="n">
         <v>78029</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521777</v>
+        <v>522015</v>
       </c>
       <c r="R3" t="n">
-        <v>6832877</v>
+        <v>6832760</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031210</v>
+        <v>122031796</v>
       </c>
       <c r="B4" t="n">
-        <v>78029</v>
+        <v>78381</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522015</v>
+        <v>521949</v>
       </c>
       <c r="R4" t="n">
-        <v>6832760</v>
+        <v>6832879</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122031796</v>
+        <v>122031681</v>
       </c>
       <c r="B5" t="n">
-        <v>78381</v>
+        <v>78029</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521949</v>
+        <v>521777</v>
       </c>
       <c r="R5" t="n">
-        <v>6832879</v>
+        <v>6832877</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 53513-2019 artfynd.xlsx
+++ b/artfynd/A 53513-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031540</v>
+        <v>122031210</v>
       </c>
       <c r="B2" t="n">
-        <v>78382</v>
+        <v>78030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521949</v>
+        <v>522015</v>
       </c>
       <c r="R2" t="n">
-        <v>6832878</v>
+        <v>6832760</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031210</v>
+        <v>122031540</v>
       </c>
       <c r="B3" t="n">
-        <v>78029</v>
+        <v>78383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522015</v>
+        <v>521949</v>
       </c>
       <c r="R3" t="n">
-        <v>6832760</v>
+        <v>6832878</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031796</v>
+        <v>122031596</v>
       </c>
       <c r="B4" t="n">
-        <v>78381</v>
+        <v>79727</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521949</v>
+        <v>521826</v>
       </c>
       <c r="R4" t="n">
-        <v>6832879</v>
+        <v>6832717</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,7 +1011,7 @@
         <v>122031681</v>
       </c>
       <c r="B5" t="n">
-        <v>78029</v>
+        <v>78030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122031596</v>
+        <v>122031796</v>
       </c>
       <c r="B6" t="n">
-        <v>79726</v>
+        <v>78382</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521826</v>
+        <v>521949</v>
       </c>
       <c r="R6" t="n">
-        <v>6832717</v>
+        <v>6832879</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 53513-2019 artfynd.xlsx
+++ b/artfynd/A 53513-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031210</v>
+        <v>122031540</v>
       </c>
       <c r="B2" t="n">
-        <v>78030</v>
+        <v>78383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522015</v>
+        <v>521949</v>
       </c>
       <c r="R2" t="n">
-        <v>6832760</v>
+        <v>6832878</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031540</v>
+        <v>122031796</v>
       </c>
       <c r="B3" t="n">
-        <v>78383</v>
+        <v>78382</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,7 +833,7 @@
         <v>521949</v>
       </c>
       <c r="R3" t="n">
-        <v>6832878</v>
+        <v>6832879</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031596</v>
+        <v>122031681</v>
       </c>
       <c r="B4" t="n">
-        <v>79727</v>
+        <v>78030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521826</v>
+        <v>521777</v>
       </c>
       <c r="R4" t="n">
-        <v>6832717</v>
+        <v>6832877</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122031681</v>
+        <v>122031596</v>
       </c>
       <c r="B5" t="n">
-        <v>78030</v>
+        <v>79727</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521777</v>
+        <v>521826</v>
       </c>
       <c r="R5" t="n">
-        <v>6832877</v>
+        <v>6832717</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122031796</v>
+        <v>122031210</v>
       </c>
       <c r="B6" t="n">
-        <v>78382</v>
+        <v>78030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521949</v>
+        <v>522015</v>
       </c>
       <c r="R6" t="n">
-        <v>6832879</v>
+        <v>6832760</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 53513-2019 artfynd.xlsx
+++ b/artfynd/A 53513-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031540</v>
+        <v>122031681</v>
       </c>
       <c r="B2" t="n">
-        <v>78383</v>
+        <v>78035</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521949</v>
+        <v>521777</v>
       </c>
       <c r="R2" t="n">
-        <v>6832878</v>
+        <v>6832877</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,7 +789,7 @@
         <v>122031796</v>
       </c>
       <c r="B3" t="n">
-        <v>78382</v>
+        <v>78387</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031681</v>
+        <v>122031540</v>
       </c>
       <c r="B4" t="n">
-        <v>78030</v>
+        <v>78388</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521777</v>
+        <v>521949</v>
       </c>
       <c r="R4" t="n">
-        <v>6832877</v>
+        <v>6832878</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,7 +1011,7 @@
         <v>122031596</v>
       </c>
       <c r="B5" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>122031210</v>
       </c>
       <c r="B6" t="n">
-        <v>78030</v>
+        <v>78035</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 53513-2019 artfynd.xlsx
+++ b/artfynd/A 53513-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031681</v>
+        <v>122031596</v>
       </c>
       <c r="B2" t="n">
-        <v>78035</v>
+        <v>79732</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521777</v>
+        <v>521826</v>
       </c>
       <c r="R2" t="n">
-        <v>6832877</v>
+        <v>6832717</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031796</v>
+        <v>122031540</v>
       </c>
       <c r="B3" t="n">
-        <v>78387</v>
+        <v>78388</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,7 +833,7 @@
         <v>521949</v>
       </c>
       <c r="R3" t="n">
-        <v>6832879</v>
+        <v>6832878</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031540</v>
+        <v>122031796</v>
       </c>
       <c r="B4" t="n">
-        <v>78388</v>
+        <v>78387</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -944,7 +944,7 @@
         <v>521949</v>
       </c>
       <c r="R4" t="n">
-        <v>6832878</v>
+        <v>6832879</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122031596</v>
+        <v>122031210</v>
       </c>
       <c r="B5" t="n">
-        <v>79732</v>
+        <v>78035</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521826</v>
+        <v>522015</v>
       </c>
       <c r="R5" t="n">
-        <v>6832717</v>
+        <v>6832760</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122031210</v>
+        <v>122031681</v>
       </c>
       <c r="B6" t="n">
         <v>78035</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522015</v>
+        <v>521777</v>
       </c>
       <c r="R6" t="n">
-        <v>6832760</v>
+        <v>6832877</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
